--- a/output/姫路夢前町_日生学園跡地_収支試算.xlsx
+++ b/output/姫路夢前町_日生学園跡地_収支試算.xlsx
@@ -2156,7 +2156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2353,85 +2353,103 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>太陽光（運動場4.2haの地代・建物は残置）</t>
+          <t>既存校舎GPU DC（ハイレゾ型・高圧2MW未満・借主改修）</t>
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>0.1625116666666667</v>
+        <v>4.48</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>0.009750699999999999</v>
+        <v>0.4384</v>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>固都税を地代が辛うじて上回る水準。系統空き容量の確認要</t>
+          <t>解体・開発許可不要。特高DCのPhase 0にもなる。運営事業者の賃料負担力が低い点が制約</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>系統用蓄電池（2.5ha地代・残地未利用）</t>
+          <t>太陽光（運動場4.2haの地代・建物は残置）</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>2.306666666666667</v>
+        <v>0.1625116666666667</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>0.1384</v>
+        <v>0.009750699999999999</v>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>運動場の一部で成立。特高接続が前提で、DCと同じ電力論点</t>
+          <t>固都税を地代が辛うじて上回る水準。系統空き容量の確認要</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>産業用地分譲（平場11haを工場・倉庫用地に）</t>
+          <t>系統用蓄電池（2.5ha地代・残地未利用）</t>
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>-3.110954800473861</v>
+        <v>2.306666666666667</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>0</v>
+        <v>0.1384</v>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>売上11.1億から解体・造成・利益15%を引いた残余。開発許可（1ha超）要</t>
+          <t>運動場の一部で成立。特高接続が前提で、DCと同じ電力論点</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>産業用地分譲（平場11haを工場・倉庫用地に）</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="n">
+        <v>-3.110954800473861</v>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>売上11.1億から解体・造成・利益15%を引いた残余。開発許可（1ha超）要</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>山林・現況保有</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B17" s="12" t="n">
         <v>0.779549</v>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C17" s="12" t="n">
         <v>-0.0616</v>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>地目山林・原野の素地価格</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>募集価格</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
+      <c r="B19" s="16" t="n">
         <v>16.5</v>
       </c>
-      <c r="C18" s="7" t="n">
+      <c r="C19" s="7" t="n">
         <v>4912.207977050641</v>
       </c>
     </row>
